--- a/backend/data/financials_by_company/1087.HK.xlsx
+++ b/backend/data/financials_by_company/1087.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,567 +654,630 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-343136.906999</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.044448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-25892000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>763000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-7720000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28073000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>408597000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-25129000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-53202000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-12602000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>13303000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-47689136.906999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>495589000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>196569271</v>
-      </c>
-      <c r="S2" t="n">
-        <v>196569271</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.3233</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.3233</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-63549000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>-63549000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2956000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-66505000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-16625000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-7720000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-763000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-12602000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>13303000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-29558000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>86992000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>88021000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>26010000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>62011000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>57434000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>408597000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>466031000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>466031000</v>
-      </c>
+        <v>4153000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>1329000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>900000</v>
+        <v>17750</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2115000</v>
+        <v>2492000</v>
       </c>
       <c r="E3" t="n">
-        <v>3600000</v>
+        <v>71000</v>
       </c>
       <c r="F3" t="n">
-        <v>3600000</v>
+        <v>71000</v>
       </c>
       <c r="G3" t="n">
-        <v>-41229000</v>
+        <v>-35882000</v>
       </c>
       <c r="H3" t="n">
-        <v>28530000</v>
+        <v>27123000</v>
       </c>
       <c r="I3" t="n">
-        <v>491313000</v>
+        <v>471308000</v>
       </c>
       <c r="J3" t="n">
-        <v>5715000</v>
+        <v>2563000</v>
       </c>
       <c r="K3" t="n">
-        <v>-22815000</v>
+        <v>-24560000</v>
       </c>
       <c r="L3" t="n">
-        <v>-10294000</v>
+        <v>-3924000</v>
       </c>
       <c r="M3" t="n">
-        <v>10704000</v>
+        <v>4249000</v>
       </c>
       <c r="N3" t="n">
-        <v>410000</v>
+        <v>325000</v>
       </c>
       <c r="O3" t="n">
-        <v>-43929000</v>
+        <v>-35935250</v>
       </c>
       <c r="P3" t="n">
-        <v>-41229000</v>
+        <v>-35882000</v>
       </c>
       <c r="Q3" t="n">
-        <v>579817000</v>
+        <v>567465000</v>
       </c>
       <c r="R3" t="n">
-        <v>142655641</v>
+        <v>134431978</v>
       </c>
       <c r="S3" t="n">
-        <v>142655641</v>
+        <v>134431978</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.289</v>
+        <v>-0.2669</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.289</v>
+        <v>-0.2669</v>
       </c>
       <c r="V3" t="n">
-        <v>-41229000</v>
+        <v>-35882000</v>
       </c>
       <c r="W3" t="n">
-        <v>-41229000</v>
+        <v>-35882000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-41229000</v>
+        <v>-35882000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-5808000</v>
+        <v>-2863000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-35421000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>-33019000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>-35421000</v>
+        <v>-33019000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1902000</v>
+        <v>4210000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-33519000</v>
+        <v>-28809000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8019000</v>
+        <v>-14170000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2807000</v>
+        <v>-5025000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2807000</v>
+        <v>5025000</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-10294000</v>
+        <v>-3924000</v>
       </c>
       <c r="AK3" t="n">
-        <v>10704000</v>
+        <v>4249000</v>
       </c>
       <c r="AL3" t="n">
-        <v>410000</v>
+        <v>325000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-18806000</v>
+        <v>-10786000</v>
       </c>
       <c r="AN3" t="n">
-        <v>88504000</v>
+        <v>96157000</v>
       </c>
       <c r="AO3" t="n">
-        <v>89731000</v>
+        <v>97217000</v>
       </c>
       <c r="AP3" t="n">
-        <v>27440000</v>
+        <v>28709000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>62291000</v>
+        <v>68508000</v>
       </c>
       <c r="AR3" t="n">
-        <v>69698000</v>
+        <v>85371000</v>
       </c>
       <c r="AS3" t="n">
-        <v>491313000</v>
+        <v>471308000</v>
       </c>
       <c r="AT3" t="n">
-        <v>561011000</v>
+        <v>556679000</v>
       </c>
       <c r="AU3" t="n">
-        <v>561011000</v>
-      </c>
+        <v>556679000</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>17750</v>
+        <v>900000</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>2492000</v>
+        <v>2115000</v>
       </c>
       <c r="E4" t="n">
-        <v>71000</v>
+        <v>3600000</v>
       </c>
       <c r="F4" t="n">
-        <v>71000</v>
+        <v>3600000</v>
       </c>
       <c r="G4" t="n">
-        <v>-35882000</v>
+        <v>-41229000</v>
       </c>
       <c r="H4" t="n">
-        <v>27123000</v>
+        <v>28530000</v>
       </c>
       <c r="I4" t="n">
-        <v>471308000</v>
+        <v>491313000</v>
       </c>
       <c r="J4" t="n">
-        <v>2563000</v>
+        <v>5715000</v>
       </c>
       <c r="K4" t="n">
-        <v>-24560000</v>
+        <v>-22815000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3924000</v>
+        <v>-10294000</v>
       </c>
       <c r="M4" t="n">
-        <v>4249000</v>
+        <v>10704000</v>
       </c>
       <c r="N4" t="n">
-        <v>325000</v>
+        <v>410000</v>
       </c>
       <c r="O4" t="n">
-        <v>-35935250</v>
+        <v>-43929000</v>
       </c>
       <c r="P4" t="n">
-        <v>-35882000</v>
+        <v>-41229000</v>
       </c>
       <c r="Q4" t="n">
-        <v>567465000</v>
+        <v>579817000</v>
       </c>
       <c r="R4" t="n">
-        <v>134431978</v>
+        <v>142655641</v>
       </c>
       <c r="S4" t="n">
-        <v>134431978</v>
+        <v>142655641</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2669</v>
+        <v>-0.289</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2669</v>
+        <v>-0.289</v>
       </c>
       <c r="V4" t="n">
-        <v>-35882000</v>
+        <v>-41229000</v>
       </c>
       <c r="W4" t="n">
-        <v>-35882000</v>
+        <v>-41229000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-35882000</v>
+        <v>-41229000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2863000</v>
+        <v>-5808000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-33019000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>-35421000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-33019000</v>
+        <v>-35421000</v>
       </c>
       <c r="AD4" t="n">
-        <v>4210000</v>
+        <v>1902000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-28809000</v>
+        <v>-33519000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-14170000</v>
+        <v>-8019000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5025000</v>
+        <v>2807000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5025000</v>
+        <v>-2807000</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-3924000</v>
+        <v>-10294000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4249000</v>
+        <v>10704000</v>
       </c>
       <c r="AL4" t="n">
-        <v>325000</v>
+        <v>410000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-10786000</v>
+        <v>-18806000</v>
       </c>
       <c r="AN4" t="n">
-        <v>96157000</v>
+        <v>88504000</v>
       </c>
       <c r="AO4" t="n">
-        <v>97217000</v>
+        <v>89731000</v>
       </c>
       <c r="AP4" t="n">
-        <v>28709000</v>
+        <v>27440000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>68508000</v>
+        <v>62291000</v>
       </c>
       <c r="AR4" t="n">
-        <v>85371000</v>
+        <v>69698000</v>
       </c>
       <c r="AS4" t="n">
-        <v>471308000</v>
+        <v>491313000</v>
       </c>
       <c r="AT4" t="n">
-        <v>556679000</v>
+        <v>561011000</v>
       </c>
       <c r="AU4" t="n">
-        <v>556679000</v>
-      </c>
+        <v>561011000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>544000</v>
+        <v>-343136.906999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.044448</v>
       </c>
       <c r="D5" t="n">
-        <v>5677000</v>
+        <v>-46137000</v>
       </c>
       <c r="E5" t="n">
-        <v>2176000</v>
+        <v>763000</v>
       </c>
       <c r="F5" t="n">
-        <v>2176000</v>
+        <v>-7720000</v>
       </c>
       <c r="G5" t="n">
-        <v>-18176000</v>
+        <v>-63549000</v>
       </c>
       <c r="H5" t="n">
-        <v>26894000</v>
+        <v>7828000</v>
       </c>
       <c r="I5" t="n">
-        <v>427490000</v>
+        <v>408597000</v>
       </c>
       <c r="J5" t="n">
-        <v>7853000</v>
+        <v>-45374000</v>
       </c>
       <c r="K5" t="n">
-        <v>-19041000</v>
+        <v>-53202000</v>
       </c>
       <c r="L5" t="n">
-        <v>-2543000</v>
+        <v>-12602000</v>
       </c>
       <c r="M5" t="n">
-        <v>3007000</v>
+        <v>13303000</v>
       </c>
       <c r="N5" t="n">
-        <v>464000</v>
+        <v>701000</v>
       </c>
       <c r="O5" t="n">
-        <v>-19808000</v>
+        <v>-47689136.906999</v>
       </c>
       <c r="P5" t="n">
-        <v>-16847000</v>
+        <v>-63549000</v>
       </c>
       <c r="Q5" t="n">
-        <v>506180000</v>
+        <v>495589000</v>
       </c>
       <c r="R5" t="n">
-        <v>80090254</v>
+        <v>196569271</v>
       </c>
       <c r="S5" t="n">
-        <v>80090254</v>
+        <v>196569271</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2103</v>
+        <v>-0.3233</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2103</v>
+        <v>-0.3233</v>
       </c>
       <c r="V5" t="n">
-        <v>-16847000</v>
+        <v>-63549000</v>
       </c>
       <c r="W5" t="n">
-        <v>-16847000</v>
+        <v>-63549000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16847000</v>
+        <v>-63549000</v>
       </c>
       <c r="Z5" t="n">
-        <v>4153000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-21000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1329000</v>
-      </c>
+        <v>-63549000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-22329000</v>
+        <v>-63549000</v>
       </c>
       <c r="AD5" t="n">
-        <v>281000</v>
+        <v>-2956000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-22048000</v>
+        <v>-66505000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-99000</v>
+        <v>-16625000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1136000</v>
+        <v>-7720000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1136000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
+        <v>-763000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-2543000</v>
+        <v>-12602000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3007000</v>
+        <v>13303000</v>
       </c>
       <c r="AL5" t="n">
-        <v>464000</v>
+        <v>701000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-21582000</v>
+        <v>-29558000</v>
       </c>
       <c r="AN5" t="n">
-        <v>78690000</v>
+        <v>86992000</v>
       </c>
       <c r="AO5" t="n">
-        <v>80165000</v>
+        <v>88021000</v>
       </c>
       <c r="AP5" t="n">
-        <v>25806000</v>
+        <v>26010000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>54359000</v>
+        <v>62011000</v>
       </c>
       <c r="AR5" t="n">
-        <v>57108000</v>
+        <v>57434000</v>
       </c>
       <c r="AS5" t="n">
-        <v>427490000</v>
+        <v>408597000</v>
       </c>
       <c r="AT5" t="n">
-        <v>484598000</v>
+        <v>466031000</v>
       </c>
       <c r="AU5" t="n">
-        <v>484598000</v>
+        <v>466031000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-2746587.95864</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.146782</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-43626000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4776000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-18712000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6129000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>501287000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-38850000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-44979000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-12212000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12855000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>643000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-9891587.95864</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>583380000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>199888000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>199888000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2469</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.2469</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-49345000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8489000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-57834000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-10459000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-19546000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-814000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-12212000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>12855000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>643000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-16451000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>82093000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>83602000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>25902000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>57700000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>65642000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>501287000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>566929000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>566929000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-3128000</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,782 +1623,858 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>199888000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>199888000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>135134000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>229604000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>68225000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>433048000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-10742000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>68225000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8964000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>212408000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>215039000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>212408000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>212408000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>12682000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-189678000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>866632000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13427000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>13427000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>469611000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9691000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>2657000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7034000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4403000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2631000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>459920000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>222570000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4561000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>218009000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>180710000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8078000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>25069000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>147563000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>682019000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>232841000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>4162000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>11023000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>6551000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>2831000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>11023000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>63806000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>144183000</v>
-      </c>
+        <v>40086000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>17714000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>126469000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9667000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-6068000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15735000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3927000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1122000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10686000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>449178000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>25409000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>10122000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10122000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>203139000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>122988000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-9194000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>132182000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>87520000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>2014000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>85506000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>85506000</v>
-      </c>
+        <v>78448000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>54209000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>1206000</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>140688000</v>
+        <v>117240000</v>
       </c>
       <c r="C3" t="n">
-        <v>140688000</v>
+        <v>117240000</v>
       </c>
       <c r="D3" t="n">
-        <v>142605000</v>
+        <v>21395000</v>
       </c>
       <c r="E3" t="n">
-        <v>232625000</v>
+        <v>94543000</v>
       </c>
       <c r="F3" t="n">
-        <v>93922000</v>
+        <v>116081000</v>
       </c>
       <c r="G3" t="n">
-        <v>485634000</v>
+        <v>390067000</v>
       </c>
       <c r="H3" t="n">
-        <v>-2386000</v>
+        <v>113031000</v>
       </c>
       <c r="I3" t="n">
-        <v>93922000</v>
+        <v>116081000</v>
       </c>
       <c r="J3" t="n">
-        <v>13824000</v>
+        <v>13712000</v>
       </c>
       <c r="K3" t="n">
-        <v>266833000</v>
+        <v>309236000</v>
       </c>
       <c r="L3" t="n">
-        <v>266833000</v>
+        <v>336336000</v>
       </c>
       <c r="M3" t="n">
-        <v>266833000</v>
+        <v>320093000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10857000</v>
       </c>
       <c r="O3" t="n">
-        <v>266833000</v>
+        <v>309236000</v>
       </c>
       <c r="P3" t="n">
         <v>22795000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-135320000</v>
+        <v>-92662000</v>
       </c>
       <c r="R3" t="n">
-        <v>861085000</v>
+        <v>858993000</v>
       </c>
       <c r="S3" t="n">
-        <v>9221000</v>
+        <v>7553000</v>
       </c>
       <c r="T3" t="n">
-        <v>9221000</v>
+        <v>7553000</v>
       </c>
       <c r="U3" t="n">
-        <v>479567000</v>
+        <v>426319000</v>
       </c>
       <c r="V3" t="n">
-        <v>12555000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>43699000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="n">
-        <v>5693000</v>
+        <v>8730000</v>
       </c>
       <c r="Y3" t="n">
-        <v>6862000</v>
+        <v>34969000</v>
       </c>
       <c r="Z3" t="n">
-        <v>6862000</v>
+        <v>7869000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>27100000</v>
       </c>
       <c r="AB3" t="n">
-        <v>467012000</v>
+        <v>382620000</v>
       </c>
       <c r="AC3" t="n">
-        <v>225763000</v>
+        <v>59574000</v>
       </c>
       <c r="AD3" t="n">
-        <v>6962000</v>
+        <v>5843000</v>
       </c>
       <c r="AE3" t="n">
-        <v>218801000</v>
+        <v>53731000</v>
       </c>
       <c r="AF3" t="n">
-        <v>206430000</v>
+        <v>249587000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10423000</v>
+        <v>13227000</v>
       </c>
       <c r="AH3" t="n">
-        <v>27348000</v>
+        <v>21130000</v>
       </c>
       <c r="AI3" t="n">
-        <v>168659000</v>
+        <v>215230000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>746400000</v>
+        <v>746412000</v>
       </c>
       <c r="AK3" t="n">
-        <v>281774000</v>
+        <v>250761000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>15548000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3932000</v>
+        <v>3501000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12939000</v>
+        <v>18368000</v>
       </c>
       <c r="AO3" t="n">
-        <v>12939000</v>
+        <v>18368000</v>
       </c>
       <c r="AP3" t="n">
-        <v>77575000</v>
+        <v>5528000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>172911000</v>
+        <v>193155000</v>
       </c>
       <c r="AR3" t="n">
-        <v>37959000</v>
+        <v>58203000</v>
       </c>
       <c r="AS3" t="n">
         <v>134952000</v>
       </c>
       <c r="AT3" t="n">
-        <v>14417000</v>
+        <v>14661000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-5380000</v>
+        <v>-4335000</v>
       </c>
       <c r="AV3" t="n">
-        <v>19797000</v>
+        <v>18996000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3718000</v>
+        <v>3158000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1121000</v>
+        <v>1099000</v>
       </c>
       <c r="AY3" t="n">
-        <v>14958000</v>
+        <v>14739000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>464626000</v>
+        <v>495651000</v>
       </c>
       <c r="BB3" t="n">
-        <v>24781000</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>25549000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>57470000</v>
+      </c>
       <c r="BD3" t="n">
-        <v>16053000</v>
+        <v>20336000</v>
       </c>
       <c r="BE3" t="n">
-        <v>16053000</v>
+        <v>20336000</v>
       </c>
       <c r="BF3" t="n">
-        <v>176482000</v>
+        <v>121106000</v>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>162882000</v>
+        <v>254502000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-10102000</v>
+        <v>-13498000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>172984000</v>
+        <v>268000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>84428000</v>
+        <v>74158000</v>
       </c>
       <c r="BL3" t="n">
-        <v>8232000</v>
+        <v>14722000</v>
       </c>
       <c r="BM3" t="n">
-        <v>76196000</v>
+        <v>59436000</v>
       </c>
       <c r="BN3" t="n">
-        <v>76196000</v>
+        <v>59436000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>117240000</v>
+        <v>140688000</v>
       </c>
       <c r="C4" t="n">
-        <v>117240000</v>
+        <v>140688000</v>
       </c>
       <c r="D4" t="n">
-        <v>21395000</v>
+        <v>142605000</v>
       </c>
       <c r="E4" t="n">
-        <v>94543000</v>
+        <v>232625000</v>
       </c>
       <c r="F4" t="n">
-        <v>116081000</v>
+        <v>93922000</v>
       </c>
       <c r="G4" t="n">
-        <v>390067000</v>
+        <v>485634000</v>
       </c>
       <c r="H4" t="n">
-        <v>113031000</v>
+        <v>-2386000</v>
       </c>
       <c r="I4" t="n">
-        <v>116081000</v>
+        <v>93922000</v>
       </c>
       <c r="J4" t="n">
-        <v>13712000</v>
+        <v>13824000</v>
       </c>
       <c r="K4" t="n">
-        <v>309236000</v>
+        <v>266833000</v>
       </c>
       <c r="L4" t="n">
-        <v>336336000</v>
+        <v>266833000</v>
       </c>
       <c r="M4" t="n">
-        <v>320093000</v>
+        <v>266833000</v>
       </c>
       <c r="N4" t="n">
-        <v>10857000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>309236000</v>
+        <v>266833000</v>
       </c>
       <c r="P4" t="n">
         <v>22795000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-92662000</v>
+        <v>-135320000</v>
       </c>
       <c r="R4" t="n">
-        <v>858993000</v>
+        <v>861085000</v>
       </c>
       <c r="S4" t="n">
-        <v>7553000</v>
+        <v>9221000</v>
       </c>
       <c r="T4" t="n">
-        <v>7553000</v>
+        <v>9221000</v>
       </c>
       <c r="U4" t="n">
-        <v>426319000</v>
+        <v>479567000</v>
       </c>
       <c r="V4" t="n">
-        <v>43699000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+        <v>12555000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>8730000</v>
+        <v>5693000</v>
       </c>
       <c r="Y4" t="n">
-        <v>34969000</v>
+        <v>6862000</v>
       </c>
       <c r="Z4" t="n">
-        <v>7869000</v>
+        <v>6862000</v>
       </c>
       <c r="AA4" t="n">
-        <v>27100000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>382620000</v>
+        <v>467012000</v>
       </c>
       <c r="AC4" t="n">
-        <v>59574000</v>
+        <v>225763000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5843000</v>
+        <v>6962000</v>
       </c>
       <c r="AE4" t="n">
-        <v>53731000</v>
+        <v>218801000</v>
       </c>
       <c r="AF4" t="n">
-        <v>249587000</v>
+        <v>206430000</v>
       </c>
       <c r="AG4" t="n">
-        <v>13227000</v>
+        <v>10423000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21130000</v>
+        <v>27348000</v>
       </c>
       <c r="AI4" t="n">
-        <v>215230000</v>
+        <v>168659000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>746412000</v>
+        <v>746400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>250761000</v>
+        <v>281774000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15548000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>3501000</v>
+        <v>3932000</v>
       </c>
       <c r="AN4" t="n">
-        <v>18368000</v>
+        <v>12939000</v>
       </c>
       <c r="AO4" t="n">
-        <v>18368000</v>
+        <v>12939000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5528000</v>
+        <v>77575000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>193155000</v>
+        <v>172911000</v>
       </c>
       <c r="AR4" t="n">
-        <v>58203000</v>
+        <v>37959000</v>
       </c>
       <c r="AS4" t="n">
         <v>134952000</v>
       </c>
       <c r="AT4" t="n">
-        <v>14661000</v>
+        <v>14417000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-4335000</v>
+        <v>-5380000</v>
       </c>
       <c r="AV4" t="n">
-        <v>18996000</v>
+        <v>19797000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3158000</v>
+        <v>3718000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1099000</v>
+        <v>1121000</v>
       </c>
       <c r="AY4" t="n">
-        <v>14739000</v>
+        <v>14958000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>495651000</v>
+        <v>464626000</v>
       </c>
       <c r="BB4" t="n">
-        <v>25549000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>57470000</v>
-      </c>
+        <v>24781000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>20336000</v>
+        <v>16053000</v>
       </c>
       <c r="BE4" t="n">
-        <v>20336000</v>
+        <v>16053000</v>
       </c>
       <c r="BF4" t="n">
-        <v>121106000</v>
+        <v>176482000</v>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>254502000</v>
+        <v>162882000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-13498000</v>
+        <v>-10102000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>268000000</v>
+        <v>172984000</v>
       </c>
       <c r="BK4" t="n">
-        <v>74158000</v>
+        <v>84428000</v>
       </c>
       <c r="BL4" t="n">
-        <v>14722000</v>
+        <v>8232000</v>
       </c>
       <c r="BM4" t="n">
-        <v>59436000</v>
+        <v>76196000</v>
       </c>
       <c r="BN4" t="n">
-        <v>59436000</v>
+        <v>76196000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>84240000</v>
+        <v>199888000</v>
       </c>
       <c r="C5" t="n">
-        <v>84240000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>199888000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>136223000</v>
+      </c>
       <c r="E5" t="n">
-        <v>70940000</v>
+        <v>230693000</v>
       </c>
       <c r="F5" t="n">
-        <v>109350000</v>
+        <v>68225000</v>
       </c>
       <c r="G5" t="n">
-        <v>373729000</v>
+        <v>434137000</v>
       </c>
       <c r="H5" t="n">
-        <v>101470000</v>
+        <v>-10742000</v>
       </c>
       <c r="I5" t="n">
-        <v>109350000</v>
+        <v>68225000</v>
       </c>
       <c r="J5" t="n">
-        <v>19961000</v>
+        <v>8964000</v>
       </c>
       <c r="K5" t="n">
-        <v>322750000</v>
+        <v>212408000</v>
       </c>
       <c r="L5" t="n">
-        <v>344422000</v>
+        <v>215039000</v>
       </c>
       <c r="M5" t="n">
-        <v>329301000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6551000</v>
-      </c>
+        <v>212408000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>322750000</v>
+        <v>212408000</v>
       </c>
       <c r="P5" t="n">
-        <v>21233000</v>
+        <v>12682000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-53763000</v>
+        <v>-189678000</v>
       </c>
       <c r="R5" t="n">
-        <v>822234000</v>
+        <v>866632000</v>
       </c>
       <c r="S5" t="n">
-        <v>5464000</v>
+        <v>13427000</v>
       </c>
       <c r="T5" t="n">
-        <v>5464000</v>
+        <v>13427000</v>
       </c>
       <c r="U5" t="n">
-        <v>326128000</v>
+        <v>469611000</v>
       </c>
       <c r="V5" t="n">
-        <v>49192000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2831000</v>
-      </c>
+        <v>9691000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>11768000</v>
+        <v>2657000</v>
       </c>
       <c r="Y5" t="n">
-        <v>34593000</v>
+        <v>7034000</v>
       </c>
       <c r="Z5" t="n">
-        <v>12921000</v>
+        <v>4403000</v>
       </c>
       <c r="AA5" t="n">
-        <v>21672000</v>
+        <v>2631000</v>
       </c>
       <c r="AB5" t="n">
-        <v>276936000</v>
+        <v>459920000</v>
       </c>
       <c r="AC5" t="n">
-        <v>36347000</v>
+        <v>223659000</v>
       </c>
       <c r="AD5" t="n">
-        <v>7040000</v>
+        <v>4561000</v>
       </c>
       <c r="AE5" t="n">
-        <v>29307000</v>
+        <v>219098000</v>
       </c>
       <c r="AF5" t="n">
-        <v>201927000</v>
+        <v>179621000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10484000</v>
+        <v>6989000</v>
       </c>
       <c r="AH5" t="n">
-        <v>16611000</v>
+        <v>25069000</v>
       </c>
       <c r="AI5" t="n">
-        <v>174832000</v>
+        <v>147563000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>655429000</v>
+        <v>682019000</v>
       </c>
       <c r="AK5" t="n">
-        <v>277023000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>232841000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>3718000</v>
+        <v>4162000</v>
       </c>
       <c r="AN5" t="n">
-        <v>40086000</v>
+        <v>11023000</v>
       </c>
       <c r="AO5" t="n">
-        <v>40086000</v>
+        <v>11023000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>63806000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>213400000</v>
+        <v>144183000</v>
       </c>
       <c r="AR5" t="n">
-        <v>78448000</v>
+        <v>17714000</v>
       </c>
       <c r="AS5" t="n">
-        <v>134952000</v>
+        <v>126469000</v>
       </c>
       <c r="AT5" t="n">
-        <v>19819000</v>
+        <v>9667000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-3108000</v>
+        <v>-6068000</v>
       </c>
       <c r="AV5" t="n">
-        <v>22927000</v>
+        <v>15735000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2631000</v>
+        <v>3927000</v>
       </c>
       <c r="AX5" t="n">
-        <v>656000</v>
+        <v>1122000</v>
       </c>
       <c r="AY5" t="n">
-        <v>19640000</v>
+        <v>10686000</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>378406000</v>
+        <v>449178000</v>
       </c>
       <c r="BB5" t="n">
-        <v>25765000</v>
+        <v>25409000</v>
       </c>
       <c r="BC5" t="n">
-        <v>54209000</v>
+        <v>24169000</v>
       </c>
       <c r="BD5" t="n">
-        <v>17320000</v>
+        <v>10122000</v>
       </c>
       <c r="BE5" t="n">
-        <v>17320000</v>
+        <v>10122000</v>
       </c>
       <c r="BF5" t="n">
-        <v>68191000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1206000</v>
-      </c>
+        <v>178970000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>195051000</v>
+        <v>122988000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-9156000</v>
+        <v>-9194000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>204207000</v>
+        <v>132182000</v>
       </c>
       <c r="BK5" t="n">
-        <v>70330000</v>
+        <v>87520000</v>
       </c>
       <c r="BL5" t="n">
-        <v>15410000</v>
+        <v>2014000</v>
       </c>
       <c r="BM5" t="n">
-        <v>54920000</v>
+        <v>85506000</v>
       </c>
       <c r="BN5" t="n">
-        <v>54920000</v>
+        <v>85506000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199888000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>199888000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>201775000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>261362000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62249000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>415187000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>57093000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>62249000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11405000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>165230000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>217557000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>165230000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>165230000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8377000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-811875000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>866632000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13427000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>13427000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>542476000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>59443000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>59443000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7116000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>52327000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>483033000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>201919000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4289000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>197630000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>232800000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9184000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16574000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>207042000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>707706000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>167580000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>4040000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>47525000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>102981000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>102981000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>13034000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-5709000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>18743000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3928000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1449000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>13366000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>540126000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>25988000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>42703000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18277000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>18277000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>228038000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>175785000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-8257000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>184042000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>49335000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1153000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>48182000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>48182000</v>
       </c>
     </row>
   </sheetData>
@@ -2349,7 +2488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2598,512 +2737,452 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Purchase Of Business</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>6693000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-206812000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>201007000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10223000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-947000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>85506000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>76196000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1433000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7877000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-3043000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>10223000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10223000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-5805000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-9564000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-9564000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3759000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-197248000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>201007000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3280000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>109000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3417000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3417000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>7378000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-947000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-947000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>7640000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1214000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-11973000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20635000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>16870000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-20403000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-12131000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7553000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>28746000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12602000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>897000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>28073000</v>
-      </c>
+      <c r="AC2" t="n">
+        <v>13354000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13354000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>20245000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7828000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>19016000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>-66505000</v>
-      </c>
+        <v>20243000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>657000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-1296000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-37530000</v>
+        <v>-36040000</v>
       </c>
       <c r="C3" t="n">
-        <v>-50410000</v>
+        <v>-37699000</v>
       </c>
       <c r="D3" t="n">
-        <v>144840000</v>
+        <v>69126000</v>
       </c>
       <c r="E3" t="n">
-        <v>4068000</v>
+        <v>40055000</v>
       </c>
       <c r="F3" t="n">
-        <v>-624000</v>
+        <v>-798000</v>
       </c>
       <c r="G3" t="n">
-        <v>76196000</v>
+        <v>59436000</v>
       </c>
       <c r="H3" t="n">
-        <v>59436000</v>
+        <v>54920000</v>
       </c>
       <c r="I3" t="n">
-        <v>87000</v>
+        <v>1507000</v>
       </c>
       <c r="J3" t="n">
-        <v>16673000</v>
+        <v>3009000</v>
       </c>
       <c r="K3" t="n">
-        <v>73991000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-16906000</v>
-      </c>
+        <v>63156000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>4068000</v>
+        <v>40055000</v>
       </c>
       <c r="N3" t="n">
-        <v>4068000</v>
+        <v>40055000</v>
       </c>
       <c r="O3" t="n">
-        <v>94430000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+        <v>31427000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>94430000</v>
+        <v>31427000</v>
       </c>
       <c r="S3" t="n">
-        <v>-50410000</v>
+        <v>-37699000</v>
       </c>
       <c r="T3" t="n">
-        <v>144840000</v>
+        <v>69126000</v>
       </c>
       <c r="U3" t="n">
-        <v>-20412000</v>
+        <v>-24905000</v>
       </c>
       <c r="V3" t="n">
-        <v>1354000</v>
+        <v>1877000</v>
       </c>
       <c r="W3" t="n">
-        <v>1054000</v>
+        <v>1256000</v>
       </c>
       <c r="X3" t="n">
-        <v>4064000</v>
+        <v>-20463000</v>
       </c>
       <c r="Y3" t="n">
-        <v>4064000</v>
+        <v>16821000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-37284000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-26260000</v>
+        <v>-8602000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-26260000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>-8602000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>-624000</v>
+        <v>-798000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-624000</v>
+        <v>-798000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-36906000</v>
+        <v>-35242000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3543000</v>
+        <v>-921000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-9646000</v>
+        <v>-2791000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-35564000</v>
+        <v>-48752000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-29475000</v>
+        <v>19655000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-51674000</v>
+        <v>43230000</v>
       </c>
       <c r="AM3" t="n">
-        <v>22027000</v>
+        <v>286000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4819000</v>
+        <v>-2681000</v>
       </c>
       <c r="AO3" t="n">
-        <v>18739000</v>
+        <v>-109242000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10294000</v>
+        <v>3924000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>883000</v>
+        <v>1203000</v>
       </c>
       <c r="AR3" t="n">
-        <v>28530000</v>
+        <v>27123000</v>
       </c>
       <c r="AS3" t="n">
-        <v>20244000</v>
+        <v>20245000</v>
       </c>
       <c r="AT3" t="n">
-        <v>8286000</v>
+        <v>6878000</v>
       </c>
       <c r="AU3" t="n">
-        <v>9002000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
+        <v>9091000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-33519000</v>
-      </c>
+        <v>-28809000</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-36040000</v>
+        <v>-37530000</v>
       </c>
       <c r="C4" t="n">
-        <v>-37699000</v>
+        <v>-50410000</v>
       </c>
       <c r="D4" t="n">
-        <v>69126000</v>
+        <v>144840000</v>
       </c>
       <c r="E4" t="n">
-        <v>40055000</v>
+        <v>4068000</v>
       </c>
       <c r="F4" t="n">
-        <v>-798000</v>
+        <v>-624000</v>
       </c>
       <c r="G4" t="n">
+        <v>76196000</v>
+      </c>
+      <c r="H4" t="n">
         <v>59436000</v>
       </c>
-      <c r="H4" t="n">
-        <v>54920000</v>
-      </c>
       <c r="I4" t="n">
-        <v>1507000</v>
+        <v>87000</v>
       </c>
       <c r="J4" t="n">
-        <v>3009000</v>
+        <v>16673000</v>
       </c>
       <c r="K4" t="n">
-        <v>63156000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>73991000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-16906000</v>
+      </c>
       <c r="M4" t="n">
-        <v>40055000</v>
+        <v>4068000</v>
       </c>
       <c r="N4" t="n">
-        <v>40055000</v>
+        <v>4068000</v>
       </c>
       <c r="O4" t="n">
-        <v>31427000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>94430000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
-        <v>31427000</v>
+        <v>94430000</v>
       </c>
       <c r="S4" t="n">
-        <v>-37699000</v>
+        <v>-50410000</v>
       </c>
       <c r="T4" t="n">
-        <v>69126000</v>
+        <v>144840000</v>
       </c>
       <c r="U4" t="n">
-        <v>-24905000</v>
+        <v>-20412000</v>
       </c>
       <c r="V4" t="n">
-        <v>1877000</v>
+        <v>1354000</v>
       </c>
       <c r="W4" t="n">
-        <v>1256000</v>
+        <v>1054000</v>
       </c>
       <c r="X4" t="n">
-        <v>-20463000</v>
+        <v>4064000</v>
       </c>
       <c r="Y4" t="n">
-        <v>16821000</v>
+        <v>4064000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-37284000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8602000</v>
+        <v>-26260000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-8602000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>-26260000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-798000</v>
+        <v>-624000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-798000</v>
+        <v>-624000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-35242000</v>
+        <v>-36906000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-921000</v>
+        <v>-3543000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2791000</v>
+        <v>-9646000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-48752000</v>
+        <v>-35564000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19655000</v>
+        <v>-29475000</v>
       </c>
       <c r="AL4" t="n">
-        <v>43230000</v>
+        <v>-51674000</v>
       </c>
       <c r="AM4" t="n">
-        <v>286000</v>
+        <v>22027000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2681000</v>
+        <v>4819000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-109242000</v>
+        <v>18739000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3924000</v>
+        <v>10294000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1203000</v>
+        <v>883000</v>
       </c>
       <c r="AR4" t="n">
-        <v>27123000</v>
+        <v>28530000</v>
       </c>
       <c r="AS4" t="n">
-        <v>20245000</v>
+        <v>20244000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6878000</v>
+        <v>8286000</v>
       </c>
       <c r="AU4" t="n">
-        <v>9091000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>9002000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-28809000</v>
-      </c>
+        <v>-33519000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-10553000</v>
+        <v>6693000</v>
       </c>
       <c r="C5" t="n">
-        <v>-60658000</v>
+        <v>-206812000</v>
       </c>
       <c r="D5" t="n">
-        <v>42073000</v>
+        <v>201007000</v>
       </c>
       <c r="E5" t="n">
-        <v>14455000</v>
+        <v>10223000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1846000</v>
+        <v>-947000</v>
       </c>
       <c r="G5" t="n">
-        <v>54920000</v>
+        <v>85506000</v>
       </c>
       <c r="H5" t="n">
-        <v>76128000</v>
+        <v>76196000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1178000</v>
+        <v>1433000</v>
       </c>
       <c r="J5" t="n">
-        <v>-20030000</v>
+        <v>7877000</v>
       </c>
       <c r="K5" t="n">
-        <v>-4867000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7378000</v>
-      </c>
+        <v>-3043000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>14455000</v>
+        <v>10223000</v>
       </c>
       <c r="N5" t="n">
-        <v>14455000</v>
+        <v>10223000</v>
       </c>
       <c r="O5" t="n">
-        <v>-18585000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>-5805000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-9564000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-9564000</v>
+      </c>
       <c r="R5" t="n">
-        <v>-18585000</v>
+        <v>3759000</v>
       </c>
       <c r="S5" t="n">
-        <v>-60658000</v>
+        <v>-197248000</v>
       </c>
       <c r="T5" t="n">
-        <v>42073000</v>
+        <v>201007000</v>
       </c>
       <c r="U5" t="n">
-        <v>-6456000</v>
+        <v>3280000</v>
       </c>
       <c r="V5" t="n">
-        <v>-19675000</v>
+        <v>109000</v>
       </c>
       <c r="W5" t="n">
-        <v>1711000</v>
+        <v>701000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3417000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>3417000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
@@ -3111,70 +3190,210 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>13354000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13354000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-1846000</v>
+        <v>-947000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1846000</v>
+        <v>-947000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-8707000</v>
+        <v>7640000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1714000</v>
+        <v>-1214000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3007000</v>
+        <v>-11973000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-8206000</v>
+        <v>44897000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2036000</v>
+        <v>16870000</v>
       </c>
       <c r="AL5" t="n">
-        <v>9448000</v>
+        <v>-20403000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-10469000</v>
+        <v>12131000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2064000</v>
+        <v>7553000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-7157000</v>
+        <v>28746000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2543000</v>
+        <v>12602000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>925000</v>
+        <v>897000</v>
       </c>
       <c r="AR5" t="n">
-        <v>26894000</v>
+        <v>7828000</v>
       </c>
       <c r="AS5" t="n">
-        <v>20243000</v>
+        <v>20245000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6651000</v>
+        <v>7828000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-3312000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>657000</v>
-      </c>
+        <v>19016000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-1296000</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-20719000</v>
+        <v>-66505000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-65389000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-158960000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>197242000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1791000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>48182000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>85506000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-5840000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-31484000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>33181000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>38282000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>38282000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-158960000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>197242000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1067000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-3428000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>643000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3512000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3512000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-1791000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1791000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-63598000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-142000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-12855000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-62749000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>61730000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-23464000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-9781000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-90814000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12212000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>670000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6129000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>6129000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>12085000</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>-3128000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-57834000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-3000</v>
       </c>
     </row>
   </sheetData>
@@ -3188,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EF2"/>
+  <dimension ref="A1:EE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3324,550 +3543,545 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>hasPrePostMarketData</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
       <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3939,7 +4153,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Sek Keung  Chan', 'age': 66, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 3734815, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yat Yu  Tin', 'age': 59, 'title': 'Executive Vice-Chairman', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 128587, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kei Lam  Wong CPA', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Sek Keung  Chan', 'age': 66, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 3734226, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yat Yu  Tin', 'age': 59, 'title': 'Executive Vice-Chairman', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 128567, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kei Lam  Wong CPA', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3957,403 +4171,400 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.006</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.985</v>
+        <v>48000</v>
       </c>
       <c r="AC2" t="n">
-        <v>60000</v>
+        <v>48000</v>
       </c>
       <c r="AD2" t="n">
-        <v>60000</v>
+        <v>1846081</v>
       </c>
       <c r="AE2" t="n">
-        <v>1931481</v>
+        <v>242050</v>
       </c>
       <c r="AF2" t="n">
-        <v>597200</v>
+        <v>242050</v>
       </c>
       <c r="AG2" t="n">
-        <v>597200</v>
+        <v>0.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>184696512</v>
       </c>
       <c r="AL2" t="n">
-        <v>139921600</v>
+        <v>184696512</v>
       </c>
       <c r="AM2" t="n">
-        <v>137922720</v>
+        <v>0.345</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.29</v>
+        <v>2.08</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.08</v>
+        <v>132.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>132.4</v>
+        <v>0.201</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.201</v>
+        <v>0.32578418</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.2468062</v>
+        <v>0.7423</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6909</v>
+        <v>1.045875</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.061675</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="AX2" t="b">
-        <v>0</v>
+      <c r="AW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>353222048</v>
       </c>
       <c r="AY2" t="n">
-        <v>327236608</v>
+        <v>-0.08704001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.08704001</v>
+        <v>117917929</v>
       </c>
       <c r="BA2" t="n">
-        <v>100983418</v>
+        <v>239865600</v>
       </c>
       <c r="BB2" t="n">
-        <v>199888000</v>
+        <v>0.16328</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4948</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>239865600</v>
       </c>
       <c r="BE2" t="n">
-        <v>199888000</v>
+        <v>0.9578801</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.95787334</v>
+        <v>0.8038584600000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.73078555</v>
+        <v>1767139200</v>
       </c>
       <c r="BH2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BI2" t="n">
-        <v>1798675200</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>1767139200</v>
+        <v>-49345000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-49345000</v>
-      </c>
-      <c r="BL2" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>1:20</t>
         </is>
       </c>
+      <c r="BM2" t="n">
+        <v>1627430400</v>
+      </c>
       <c r="BN2" t="n">
-        <v>1627430400</v>
+        <v>0.623</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.577</v>
+        <v>233.304</v>
       </c>
       <c r="BP2" t="n">
-        <v>216.14</v>
+        <v>0.9743589</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BS2" t="inlineStr">
+        <v>0.2568333</v>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BT2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BS2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BT2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
+      <c r="BU2" t="n">
+        <v>74047000</v>
+      </c>
       <c r="BV2" t="n">
-        <v>74047000</v>
+        <v>0.37</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.37</v>
+        <v>1514000</v>
       </c>
       <c r="BX2" t="n">
-        <v>1514000</v>
+        <v>261362000</v>
       </c>
       <c r="BY2" t="n">
-        <v>261362000</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.118</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.118</v>
+        <v>566929024</v>
       </c>
       <c r="CB2" t="n">
-        <v>566929024</v>
+        <v>158.181</v>
       </c>
       <c r="CC2" t="n">
-        <v>158.181</v>
+        <v>2.836</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.836</v>
+        <v>-0.015420001</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.015420001</v>
+        <v>-0.26133</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.26133</v>
+        <v>65642000</v>
       </c>
       <c r="CG2" t="n">
-        <v>65642000</v>
+        <v>-76987624</v>
       </c>
       <c r="CH2" t="n">
-        <v>-76987624</v>
+        <v>-63598000</v>
       </c>
       <c r="CI2" t="n">
-        <v>-63598000</v>
+        <v>0.339</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.339</v>
+        <v>0.11579</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.11579</v>
+        <v>0.0026699998</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0026699998</v>
-      </c>
-      <c r="CM2" t="n">
         <v>-0.00966</v>
       </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>1087.HK</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>1087.HK</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CT2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1289871000000</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.04000002</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.75 - 0.77</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1846081</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.42499998</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.231884</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.345 - 2.08</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.6298077</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>97.43589</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1553698740</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1553698740</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.027700007</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.03731646</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.27587497</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.26377434</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>1781769589</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>finmb_54339776</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-4.9382744</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>InvesTech Holdings Limited</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>INVESTECH HLDGS</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CY2" t="n">
-        <v>1780378769</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>finmb_54339776</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.009099960000000001</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.013171168</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.36167496</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.3406645</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>InvesTech Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1289871000000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>0.68 - 0.7</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>1931481</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1.4137931</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>0.29 - 2.08</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-1.3799999</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.6634615</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>100</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1553698740</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1553698740</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1.449274</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="EF2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
